--- a/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256604109285871</v>
+        <v>1.248985747100916</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610293982437113</v>
+        <v>4.64278001397064</v>
       </c>
       <c r="D3" t="n">
-        <v>6.044969229417259</v>
+        <v>6.103285043049519</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91186732114024</v>
+        <v>11.99505080412107</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.395900980090506</v>
+        <v>1.362350182347943</v>
       </c>
       <c r="C4" t="n">
-        <v>5.075703347354408</v>
+        <v>5.160098075196694</v>
       </c>
       <c r="D4" t="n">
-        <v>6.226829877705943</v>
+        <v>6.335370221985648</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69843420515086</v>
+        <v>12.85781847953028</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.585204908289872</v>
+        <v>1.514334803614181</v>
       </c>
       <c r="C5" t="n">
-        <v>5.665033798212058</v>
+        <v>5.809325094349544</v>
       </c>
       <c r="D5" t="n">
-        <v>6.524578767999513</v>
+        <v>6.604875872250832</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77481747450144</v>
+        <v>13.92853577021456</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.800740737787153</v>
+        <v>1.699530005105673</v>
       </c>
       <c r="C6" t="n">
-        <v>6.402371115805438</v>
+        <v>6.591600359482334</v>
       </c>
       <c r="D6" t="n">
-        <v>6.822709505898012</v>
+        <v>6.920644021327655</v>
       </c>
       <c r="E6" t="n">
-        <v>15.0258213594906</v>
+        <v>15.21177438591566</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.037824032413705</v>
+        <v>1.902070898256558</v>
       </c>
       <c r="C7" t="n">
-        <v>7.264645523140826</v>
+        <v>7.512322238480988</v>
       </c>
       <c r="D7" t="n">
-        <v>7.091302239920283</v>
+        <v>7.289656132970398</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39377179547481</v>
+        <v>16.70404926970794</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.251153697971123</v>
+        <v>1.134999875675007</v>
       </c>
       <c r="C8" t="n">
-        <v>4.912998886542269</v>
+        <v>5.159646665737017</v>
       </c>
       <c r="D8" t="n">
-        <v>5.249253803995734</v>
+        <v>5.48545740871325</v>
       </c>
       <c r="E8" t="n">
-        <v>11.41340638850913</v>
+        <v>11.78010395012527</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565186849400476</v>
+        <v>1.406634779352403</v>
       </c>
       <c r="C9" t="n">
-        <v>5.970312109937651</v>
+        <v>6.338734179174796</v>
       </c>
       <c r="D9" t="n">
-        <v>5.635964897402102</v>
+        <v>5.973709585335294</v>
       </c>
       <c r="E9" t="n">
-        <v>13.17146385674023</v>
+        <v>13.71907854386249</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.893758485540928</v>
+        <v>1.682857978945201</v>
       </c>
       <c r="C10" t="n">
-        <v>7.135264938321787</v>
+        <v>7.675060643260419</v>
       </c>
       <c r="D10" t="n">
-        <v>6.037087226635996</v>
+        <v>6.410572040993183</v>
       </c>
       <c r="E10" t="n">
-        <v>15.06611065049871</v>
+        <v>15.7684906631988</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.245161821523422</v>
+        <v>1.964622600509558</v>
       </c>
       <c r="C11" t="n">
-        <v>8.430516070641163</v>
+        <v>9.141077238669657</v>
       </c>
       <c r="D11" t="n">
-        <v>6.447559015014304</v>
+        <v>6.870708948527019</v>
       </c>
       <c r="E11" t="n">
-        <v>17.12323690717889</v>
+        <v>17.97640878770623</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.622230486917501</v>
+        <v>2.260359588307949</v>
       </c>
       <c r="C12" t="n">
-        <v>9.850431661672797</v>
+        <v>10.71055990920827</v>
       </c>
       <c r="D12" t="n">
-        <v>6.822167301596531</v>
+        <v>7.293177120394279</v>
       </c>
       <c r="E12" t="n">
-        <v>19.29482945018683</v>
+        <v>20.26409661791049</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.005124765528625</v>
+        <v>2.544410981308549</v>
       </c>
       <c r="C13" t="n">
-        <v>11.32292326281533</v>
+        <v>12.32638454005775</v>
       </c>
       <c r="D13" t="n">
-        <v>7.214669303151438</v>
+        <v>7.709488397016345</v>
       </c>
       <c r="E13" t="n">
-        <v>21.54271733149539</v>
+        <v>22.58028391838264</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.760155823990022</v>
+        <v>1.481575095432947</v>
       </c>
       <c r="C14" t="n">
-        <v>8.056162756187071</v>
+        <v>8.677432338388538</v>
       </c>
       <c r="D14" t="n">
-        <v>5.506082911883024</v>
+        <v>5.85718534335281</v>
       </c>
       <c r="E14" t="n">
-        <v>15.32240149206012</v>
+        <v>16.01619277717429</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.829192322552657</v>
+        <v>1.503526974099905</v>
       </c>
       <c r="C15" t="n">
-        <v>8.654753966420436</v>
+        <v>9.362387894164494</v>
       </c>
       <c r="D15" t="n">
-        <v>5.445479626099869</v>
+        <v>5.821557719165694</v>
       </c>
       <c r="E15" t="n">
-        <v>15.92942591507296</v>
+        <v>16.68747258743009</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.170585269227443</v>
+        <v>1.737909421011789</v>
       </c>
       <c r="C16" t="n">
-        <v>10.21059827567965</v>
+        <v>11.08311673035196</v>
       </c>
       <c r="D16" t="n">
-        <v>5.837255864956601</v>
+        <v>6.240489099521893</v>
       </c>
       <c r="E16" t="n">
-        <v>18.2184394098637</v>
+        <v>19.06151525088564</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.770238372912636</v>
+        <v>1.389457708343468</v>
       </c>
       <c r="C17" t="n">
-        <v>9.404092536640899</v>
+        <v>10.24005070680706</v>
       </c>
       <c r="D17" t="n">
-        <v>5.364053471509637</v>
+        <v>5.765028686355163</v>
       </c>
       <c r="E17" t="n">
-        <v>16.53838438106317</v>
+        <v>17.39453710150569</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.058882015438241</v>
+        <v>1.580270192140878</v>
       </c>
       <c r="C18" t="n">
-        <v>10.96907691702665</v>
+        <v>12.01941933336919</v>
       </c>
       <c r="D18" t="n">
-        <v>5.75133330588092</v>
+        <v>6.123307693542994</v>
       </c>
       <c r="E18" t="n">
-        <v>18.77929223834581</v>
+        <v>19.72299721905306</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.104444926392335</v>
+        <v>1.580918145625681</v>
       </c>
       <c r="C19" t="n">
-        <v>11.73749084514063</v>
+        <v>12.92336353205444</v>
       </c>
       <c r="D19" t="n">
-        <v>5.829470605661924</v>
+        <v>6.179286947639147</v>
       </c>
       <c r="E19" t="n">
-        <v>19.67140637719489</v>
+        <v>20.68356862531927</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.386991915674568</v>
+        <v>1.762305851462322</v>
       </c>
       <c r="C20" t="n">
-        <v>13.52297575990022</v>
+        <v>14.90114336964485</v>
       </c>
       <c r="D20" t="n">
-        <v>6.272111193075683</v>
+        <v>6.563837523392623</v>
       </c>
       <c r="E20" t="n">
-        <v>22.18207886865047</v>
+        <v>23.2272867444998</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.444622111845097</v>
+        <v>1.050411138681832</v>
       </c>
       <c r="C21" t="n">
-        <v>9.956944121333407</v>
+        <v>10.99125459766559</v>
       </c>
       <c r="D21" t="n">
-        <v>5.224910369386738</v>
+        <v>5.437547104649554</v>
       </c>
       <c r="E21" t="n">
-        <v>16.62647660256524</v>
+        <v>17.47921284099698</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248985747100916</v>
+        <v>1.248259253799773</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64278001397064</v>
+        <v>4.606013562446597</v>
       </c>
       <c r="D3" t="n">
-        <v>6.103285043049519</v>
+        <v>6.139452628473972</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99505080412107</v>
+        <v>11.99372544472034</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.362350182347943</v>
+        <v>1.370282931178384</v>
       </c>
       <c r="C4" t="n">
-        <v>5.160098075196694</v>
+        <v>5.0951075675774</v>
       </c>
       <c r="D4" t="n">
-        <v>6.335370221985648</v>
+        <v>6.407626879768816</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85781847953028</v>
+        <v>12.8730173785246</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.514334803614181</v>
+        <v>1.543656975601988</v>
       </c>
       <c r="C5" t="n">
-        <v>5.809325094349544</v>
+        <v>5.742473027200586</v>
       </c>
       <c r="D5" t="n">
-        <v>6.604875872250832</v>
+        <v>6.803639958360423</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92853577021456</v>
+        <v>14.089769961163</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.699530005105673</v>
+        <v>1.739099118284211</v>
       </c>
       <c r="C6" t="n">
-        <v>6.591600359482334</v>
+        <v>6.534310553771676</v>
       </c>
       <c r="D6" t="n">
-        <v>6.920644021327655</v>
+        <v>7.168032504285546</v>
       </c>
       <c r="E6" t="n">
-        <v>15.21177438591566</v>
+        <v>15.44144217634143</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.902070898256558</v>
+        <v>1.953430896764495</v>
       </c>
       <c r="C7" t="n">
-        <v>7.512322238480988</v>
+        <v>7.458350260622566</v>
       </c>
       <c r="D7" t="n">
-        <v>7.289656132970398</v>
+        <v>7.538048145176298</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70404926970794</v>
+        <v>16.94982930256336</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.134999875675007</v>
+        <v>1.179539918891046</v>
       </c>
       <c r="C8" t="n">
-        <v>5.159646665737017</v>
+        <v>5.12977560030764</v>
       </c>
       <c r="D8" t="n">
-        <v>5.48545740871325</v>
+        <v>5.730145653657162</v>
       </c>
       <c r="E8" t="n">
-        <v>11.78010395012527</v>
+        <v>12.03946117285585</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.406634779352403</v>
+        <v>1.469518336614979</v>
       </c>
       <c r="C9" t="n">
-        <v>6.338734179174796</v>
+        <v>6.318802397705226</v>
       </c>
       <c r="D9" t="n">
-        <v>5.973709585335294</v>
+        <v>6.251295014619027</v>
       </c>
       <c r="E9" t="n">
-        <v>13.71907854386249</v>
+        <v>14.03961574893923</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.682857978945201</v>
+        <v>1.775135062158899</v>
       </c>
       <c r="C10" t="n">
-        <v>7.675060643260419</v>
+        <v>7.741364790786243</v>
       </c>
       <c r="D10" t="n">
-        <v>6.410572040993183</v>
+        <v>6.830495427627692</v>
       </c>
       <c r="E10" t="n">
-        <v>15.7684906631988</v>
+        <v>16.34699528057283</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.964622600509558</v>
+        <v>2.087853608032005</v>
       </c>
       <c r="C11" t="n">
-        <v>9.141077238669657</v>
+        <v>9.367229324489278</v>
       </c>
       <c r="D11" t="n">
-        <v>6.870708948527019</v>
+        <v>7.410644223532149</v>
       </c>
       <c r="E11" t="n">
-        <v>17.97640878770623</v>
+        <v>18.86572715605343</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.260359588307949</v>
+        <v>2.397145005692028</v>
       </c>
       <c r="C12" t="n">
-        <v>10.71055990920827</v>
+        <v>11.11766453203412</v>
       </c>
       <c r="D12" t="n">
-        <v>7.293177120394279</v>
+        <v>8.00125933474243</v>
       </c>
       <c r="E12" t="n">
-        <v>20.26409661791049</v>
+        <v>21.51606887246858</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.544410981308549</v>
+        <v>2.679950899764429</v>
       </c>
       <c r="C13" t="n">
-        <v>12.32638454005775</v>
+        <v>12.98372840282497</v>
       </c>
       <c r="D13" t="n">
-        <v>7.709488397016345</v>
+        <v>8.591440530294044</v>
       </c>
       <c r="E13" t="n">
-        <v>22.58028391838264</v>
+        <v>24.25511983288344</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.481575095432947</v>
+        <v>1.543297573598944</v>
       </c>
       <c r="C14" t="n">
-        <v>8.677432338388538</v>
+        <v>9.141956082129958</v>
       </c>
       <c r="D14" t="n">
-        <v>5.85718534335281</v>
+        <v>6.524773782240642</v>
       </c>
       <c r="E14" t="n">
-        <v>16.01619277717429</v>
+        <v>17.21002743796954</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.503526974099905</v>
+        <v>1.556511897698106</v>
       </c>
       <c r="C15" t="n">
-        <v>9.362387894164494</v>
+        <v>10.13710464253974</v>
       </c>
       <c r="D15" t="n">
-        <v>5.821557719165694</v>
+        <v>6.600397807898774</v>
       </c>
       <c r="E15" t="n">
-        <v>16.68747258743009</v>
+        <v>18.29401434813662</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.737909421011789</v>
+        <v>1.775745977533461</v>
       </c>
       <c r="C16" t="n">
-        <v>11.08311673035196</v>
+        <v>12.16855662712132</v>
       </c>
       <c r="D16" t="n">
-        <v>6.240489099521893</v>
+        <v>7.100774977799288</v>
       </c>
       <c r="E16" t="n">
-        <v>19.06151525088564</v>
+        <v>21.04507758245407</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.389457708343468</v>
+        <v>1.405391473583394</v>
       </c>
       <c r="C17" t="n">
-        <v>10.24005070680706</v>
+        <v>11.38303083652232</v>
       </c>
       <c r="D17" t="n">
-        <v>5.765028686355163</v>
+        <v>6.628004553342194</v>
       </c>
       <c r="E17" t="n">
-        <v>17.39453710150569</v>
+        <v>19.41642686344791</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.580270192140878</v>
+        <v>1.574880397244563</v>
       </c>
       <c r="C18" t="n">
-        <v>12.01941933336919</v>
+        <v>13.40714916575318</v>
       </c>
       <c r="D18" t="n">
-        <v>6.123307693542994</v>
+        <v>7.115854622536519</v>
       </c>
       <c r="E18" t="n">
-        <v>19.72299721905306</v>
+        <v>22.09788418553427</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.580918145625681</v>
+        <v>1.551033745508408</v>
       </c>
       <c r="C19" t="n">
-        <v>12.92336353205444</v>
+        <v>14.43708104732443</v>
       </c>
       <c r="D19" t="n">
-        <v>6.179286947639147</v>
+        <v>7.217710946852126</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68356862531927</v>
+        <v>23.20582573968496</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.762305851462322</v>
+        <v>1.691620016756552</v>
       </c>
       <c r="C20" t="n">
-        <v>14.90114336964485</v>
+        <v>16.59121222502869</v>
       </c>
       <c r="D20" t="n">
-        <v>6.563837523392623</v>
+        <v>7.68216596825425</v>
       </c>
       <c r="E20" t="n">
-        <v>23.2272867444998</v>
+        <v>25.9649982100395</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.050411138681832</v>
+        <v>0.9874123885003145</v>
       </c>
       <c r="C21" t="n">
-        <v>10.99125459766559</v>
+        <v>12.16282322052852</v>
       </c>
       <c r="D21" t="n">
-        <v>5.437547104649554</v>
+        <v>6.426707004063428</v>
       </c>
       <c r="E21" t="n">
-        <v>17.47921284099698</v>
+        <v>19.57694261309226</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_62_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248259253799773</v>
+        <v>2.609583094541976</v>
       </c>
       <c r="C3" t="n">
-        <v>4.606013562446597</v>
+        <v>7.671275555570658</v>
       </c>
       <c r="D3" t="n">
-        <v>6.139452628473972</v>
+        <v>8.147139120997045</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99372544472034</v>
+        <v>18.42799777110968</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370282931178384</v>
+        <v>1.115332067372681</v>
       </c>
       <c r="C4" t="n">
-        <v>5.0951075675774</v>
+        <v>4.4316588429422</v>
       </c>
       <c r="D4" t="n">
-        <v>6.407626879768816</v>
+        <v>5.663428134475063</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8730173785246</v>
+        <v>11.21041904478994</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.543656975601988</v>
+        <v>1.245892979231419</v>
       </c>
       <c r="C5" t="n">
-        <v>5.742473027200586</v>
+        <v>5.017837107775689</v>
       </c>
       <c r="D5" t="n">
-        <v>6.803639958360423</v>
+        <v>5.880223054353698</v>
       </c>
       <c r="E5" t="n">
-        <v>14.089769961163</v>
+        <v>12.14395314136081</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739099118284211</v>
+        <v>1.388718392695726</v>
       </c>
       <c r="C6" t="n">
-        <v>6.534310553771676</v>
+        <v>5.763985610076666</v>
       </c>
       <c r="D6" t="n">
-        <v>7.168032504285546</v>
+        <v>6.160080189240139</v>
       </c>
       <c r="E6" t="n">
-        <v>15.44144217634143</v>
+        <v>13.31278419201253</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.953430896764495</v>
+        <v>1.531145071635559</v>
       </c>
       <c r="C7" t="n">
-        <v>7.458350260622566</v>
+        <v>6.691562774544559</v>
       </c>
       <c r="D7" t="n">
-        <v>7.538048145176298</v>
+        <v>6.449169714613476</v>
       </c>
       <c r="E7" t="n">
-        <v>16.94982930256336</v>
+        <v>14.67187756079359</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.179539918891046</v>
+        <v>1.685436146712545</v>
       </c>
       <c r="C8" t="n">
-        <v>5.12977560030764</v>
+        <v>7.843553240155117</v>
       </c>
       <c r="D8" t="n">
-        <v>5.730145653657162</v>
+        <v>6.749142687692395</v>
       </c>
       <c r="E8" t="n">
-        <v>12.03946117285585</v>
+        <v>16.27813207456006</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.469518336614979</v>
+        <v>1.842701765433298</v>
       </c>
       <c r="C9" t="n">
-        <v>6.318802397705226</v>
+        <v>9.171040488802788</v>
       </c>
       <c r="D9" t="n">
-        <v>6.251295014619027</v>
+        <v>7.07568868881097</v>
       </c>
       <c r="E9" t="n">
-        <v>14.03961574893923</v>
+        <v>18.08943094304706</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.775135062158899</v>
+        <v>1.14582719805758</v>
       </c>
       <c r="C10" t="n">
-        <v>7.741364790786243</v>
+        <v>6.871016562574408</v>
       </c>
       <c r="D10" t="n">
-        <v>6.830495427627692</v>
+        <v>5.566686197666179</v>
       </c>
       <c r="E10" t="n">
-        <v>16.34699528057283</v>
+        <v>13.58352995829817</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.087853608032005</v>
+        <v>1.086195842501629</v>
       </c>
       <c r="C11" t="n">
-        <v>9.367229324489278</v>
+        <v>7.44577093854866</v>
       </c>
       <c r="D11" t="n">
-        <v>7.410644223532149</v>
+        <v>5.360470092389137</v>
       </c>
       <c r="E11" t="n">
-        <v>18.86572715605343</v>
+        <v>13.89243687343943</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.397145005692028</v>
+        <v>1.178313229591107</v>
       </c>
       <c r="C12" t="n">
-        <v>11.11766453203412</v>
+        <v>8.960116772349364</v>
       </c>
       <c r="D12" t="n">
-        <v>8.00125933474243</v>
+        <v>5.702334277961961</v>
       </c>
       <c r="E12" t="n">
-        <v>21.51606887246858</v>
+        <v>15.84076427990243</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.679950899764429</v>
+        <v>0.928615518492973</v>
       </c>
       <c r="C13" t="n">
-        <v>12.98372840282497</v>
+        <v>8.673888229176208</v>
       </c>
       <c r="D13" t="n">
-        <v>8.591440530294044</v>
+        <v>5.152270856749516</v>
       </c>
       <c r="E13" t="n">
-        <v>24.25511983288344</v>
+        <v>14.7547746044187</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.543297573598944</v>
+        <v>1.012319327757056</v>
       </c>
       <c r="C14" t="n">
-        <v>9.141956082129958</v>
+        <v>10.2701118215111</v>
       </c>
       <c r="D14" t="n">
-        <v>6.524773782240642</v>
+        <v>5.426325728390013</v>
       </c>
       <c r="E14" t="n">
-        <v>17.21002743796954</v>
+        <v>16.70875687765816</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.556511897698106</v>
+        <v>0.9881290643244147</v>
       </c>
       <c r="C15" t="n">
-        <v>10.13710464253974</v>
+        <v>11.18743724140523</v>
       </c>
       <c r="D15" t="n">
-        <v>6.600397807898774</v>
+        <v>5.426757697379881</v>
       </c>
       <c r="E15" t="n">
-        <v>18.29401434813662</v>
+        <v>17.60232400310953</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.775745977533461</v>
+        <v>1.084762490853428</v>
       </c>
       <c r="C16" t="n">
-        <v>12.16855662712132</v>
+        <v>13.09977377703055</v>
       </c>
       <c r="D16" t="n">
-        <v>7.100774977799288</v>
+        <v>5.743135712550459</v>
       </c>
       <c r="E16" t="n">
-        <v>21.04507758245407</v>
+        <v>19.92767198043444</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.405391473583394</v>
+        <v>0.6541777652478197</v>
       </c>
       <c r="C17" t="n">
-        <v>11.38303083652232</v>
+        <v>9.770834209039339</v>
       </c>
       <c r="D17" t="n">
-        <v>6.628004553342194</v>
+        <v>4.730158613831557</v>
       </c>
       <c r="E17" t="n">
-        <v>19.41642686344791</v>
+        <v>15.15517058811872</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.574880397244563</v>
+        <v>0.514170725145182</v>
       </c>
       <c r="C18" t="n">
-        <v>13.40714916575318</v>
+        <v>8.7515837424903</v>
       </c>
       <c r="D18" t="n">
-        <v>7.115854622536519</v>
+        <v>4.231538772321644</v>
       </c>
       <c r="E18" t="n">
-        <v>22.09788418553427</v>
+        <v>13.49729323995713</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.551033745508408</v>
+        <v>0.604835125632375</v>
       </c>
       <c r="C19" t="n">
-        <v>14.43708104732443</v>
+        <v>10.81205618920942</v>
       </c>
       <c r="D19" t="n">
-        <v>7.217710946852126</v>
+        <v>4.6616718939833</v>
       </c>
       <c r="E19" t="n">
-        <v>23.20582573968496</v>
+        <v>16.07856320882509</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.691620016756552</v>
+        <v>0.6906791448917162</v>
       </c>
       <c r="C20" t="n">
-        <v>16.59121222502869</v>
+        <v>13.00326797770309</v>
       </c>
       <c r="D20" t="n">
-        <v>7.68216596825425</v>
+        <v>5.048843736107115</v>
       </c>
       <c r="E20" t="n">
-        <v>25.9649982100395</v>
+        <v>18.74279085870192</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9874123885003145</v>
+        <v>0.7706424954026188</v>
       </c>
       <c r="C21" t="n">
-        <v>12.16282322052852</v>
+        <v>15.16238643374493</v>
       </c>
       <c r="D21" t="n">
-        <v>6.426707004063428</v>
+        <v>5.420091630468046</v>
       </c>
       <c r="E21" t="n">
-        <v>19.57694261309226</v>
+        <v>21.35312055961559</v>
       </c>
     </row>
   </sheetData>
